--- a/RoyalBullionFund_BugReport.xlsx
+++ b/RoyalBullionFund_BugReport.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2994" uniqueCount="1938">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2934" uniqueCount="1918">
   <si>
     <t>Bug ID</t>
   </si>
@@ -34,7 +34,7 @@
     <t>Bug-002</t>
   </si>
   <si>
-    <t>Add “All Types” filter in Movement Logs (backend)</t>
+    <t>Add “All Types” filter in Movement Logs (Backend)</t>
   </si>
   <si>
     <t>Bug-003</t>
@@ -730,1512 +730,1512 @@
     <t>Bug-119</t>
   </si>
   <si>
+    <t>Remove the "Cancelled" status from the My Orders screen</t>
+  </si>
+  <si>
+    <t>Bug-120</t>
+  </si>
+  <si>
+    <t>Bug-121</t>
+  </si>
+  <si>
+    <t>Add bottom spacing on the Product Listing screen</t>
+  </si>
+  <si>
+    <t>Bug-122</t>
+  </si>
+  <si>
+    <t>Prevent adding more than the available product quantity</t>
+  </si>
+  <si>
+    <t>Bug-123</t>
+  </si>
+  <si>
+    <t>Product Details should display the default quantity and "Add to Cart" button when the cart quantity is below the maximum</t>
+  </si>
+  <si>
+    <t>Bug-124</t>
+  </si>
+  <si>
+    <t>Allow manual entry of item quantity</t>
+  </si>
+  <si>
+    <t>Bug-125</t>
+  </si>
+  <si>
+    <t>RBF balance should not be abbreviated in millions or billions</t>
+  </si>
+  <si>
+    <t>Bug-126</t>
+  </si>
+  <si>
+    <t>Display RBG amounts in grams (g) in the Wallet</t>
+  </si>
+  <si>
+    <t>Bug-127</t>
+  </si>
+  <si>
+    <t>Display a "Sort By" option before selecting a sorting method</t>
+  </si>
+  <si>
+    <t>Bug-128</t>
+  </si>
+  <si>
+    <t>Add additional sorting options to the Product filter</t>
+  </si>
+  <si>
+    <t>Bug-129</t>
+  </si>
+  <si>
+    <t>Oldest filter is not working on the Product Listing screen</t>
+  </si>
+  <si>
+    <t>Bug-130</t>
+  </si>
+  <si>
+    <t>Bug-131</t>
+  </si>
+  <si>
+    <t>Bug-132</t>
+  </si>
+  <si>
+    <t>Display the correct currency based on the product type</t>
+  </si>
+  <si>
+    <t>Bug-133</t>
+  </si>
+  <si>
+    <t>Replace USDT with RBF and RBG in the Product filter</t>
+  </si>
+  <si>
+    <t>Bug-134</t>
+  </si>
+  <si>
+    <t>Bug-135</t>
+  </si>
+  <si>
+    <t>Default price range should be 0–1000 in the Product filter</t>
+  </si>
+  <si>
+    <t>Bug-136</t>
+  </si>
+  <si>
+    <t>Bug-137</t>
+  </si>
+  <si>
+    <t>Do not display a separate Transaction ID for Conversion transactions</t>
+  </si>
+  <si>
+    <t>Bug-138</t>
+  </si>
+  <si>
+    <t>RBF RBG label is missing on the Conversion</t>
+  </si>
+  <si>
+    <t>Bug-139</t>
+  </si>
+  <si>
+    <t>User should remain logged in when navigating from Change Password to Forgot Password</t>
+  </si>
+  <si>
+    <t>Bug-140</t>
+  </si>
+  <si>
+    <t>Pre-fill email on the Forgot Password screen when navigated from Change Password</t>
+  </si>
+  <si>
+    <t>Bug-141</t>
+  </si>
+  <si>
+    <t>When navigating from the Change Password screen to the Forgot Password screen, the user's email address is pre-filled but remains editable.</t>
+  </si>
+  <si>
+    <t>Bug-142</t>
+  </si>
+  <si>
+    <t>KYC record order changes after approval or rejection by Admin</t>
+  </si>
+  <si>
+    <t>Bug-143</t>
+  </si>
+  <si>
+    <t>Long filter text breaks the UI on the Product Listing screen</t>
+  </si>
+  <si>
+    <t>Bug-144</t>
+  </si>
+  <si>
+    <t>KYC file upload accepts files larger than 5 MB</t>
+  </si>
+  <si>
+    <t>Bug-145</t>
+  </si>
+  <si>
+    <t>Add Pull-to-Refresh functionality on the KYC Details screen</t>
+  </si>
+  <si>
+    <t>Bug-146</t>
+  </si>
+  <si>
+    <t>Rejected reason is not displayed after KYC rejection</t>
+  </si>
+  <si>
+    <t>Bug-147</t>
+  </si>
+  <si>
+    <t>KYC image dimensions are incorrect on the KYC Details screen --- admin</t>
+  </si>
+  <si>
+    <t>Bug-148</t>
+  </si>
+  <si>
+    <t>KYC status should display "Pending"</t>
+  </si>
+  <si>
+    <t>Bug-149</t>
+  </si>
+  <si>
+    <t>ID should be displayed in uppercase on the KYC Details screen</t>
+  </si>
+  <si>
+    <t>Bug-150</t>
+  </si>
+  <si>
+    <t>P2P Transfer screen becomes unresponsive after navigating back</t>
+  </si>
+  <si>
+    <t>Bug-151</t>
+  </si>
+  <si>
+    <t>Incorrect initial error message is displayed on the P2P Transfer screen</t>
+  </si>
+  <si>
+    <t>Bug-152</t>
+  </si>
+  <si>
+    <t>Incorrect button text on the P2P Transfer Failed screen</t>
+  </si>
+  <si>
+    <t>Bug-153</t>
+  </si>
+  <si>
+    <t>Keyboard overlaps the text field on the Review screen</t>
+  </si>
+  <si>
+    <t>Bug-154</t>
+  </si>
+  <si>
+    <t>Incorrect conversion rate displayed as "1 RBF = 0 RBG"</t>
+  </si>
+  <si>
+    <t>Bug-155</t>
+  </si>
+  <si>
+    <t>Edit Profile screen is missing field validations</t>
+  </si>
+  <si>
+    <t>Bug-156</t>
+  </si>
+  <si>
+    <t>Apply an 8-digit input limit to Amount fields in P2P Transfer and Service Pack</t>
+  </si>
+  <si>
+    <t>Bug-157</t>
+  </si>
+  <si>
+    <t>Bug-158</t>
+  </si>
+  <si>
+    <t>Bottom navigation bar disappears after changing the password</t>
+  </si>
+  <si>
+    <t>Bug-159</t>
+  </si>
+  <si>
+    <t>Verification tick should not displays on the KYC Details screen for approved KYC</t>
+  </si>
+  <si>
+    <t>Bug-160</t>
+  </si>
+  <si>
+    <t>Session expires on the Change Password screen</t>
+  </si>
+  <si>
+    <t>Bug-161</t>
+  </si>
+  <si>
+    <t>Delivery Date should not be displayed for Prestige orders</t>
+  </si>
+  <si>
+    <t>Bug-162</t>
+  </si>
+  <si>
+    <t>Delivery Date column should not be displayed in Order Management for the Partner flow</t>
+  </si>
+  <si>
+    <t>Bug-163</t>
+  </si>
+  <si>
+    <t>Long order details should be truncated with ellipsis in Prestige Marketplace</t>
+  </si>
+  <si>
+    <t>Bug-164</t>
+  </si>
+  <si>
+    <t>Incorrect order image is displayed temporarily on the My Orders screen</t>
+  </si>
+  <si>
+    <t>Bug-165</t>
+  </si>
+  <si>
+    <t>Web application crashes when entering long text in Meeting Place and Delivery Instructions</t>
+  </si>
+  <si>
+    <t>Bug-166</t>
+  </si>
+  <si>
+    <t>Long text breaks the UI in Meeting Place and Delivery Instructions fields</t>
+  </si>
+  <si>
+    <t>Bug-167</t>
+  </si>
+  <si>
+    <t>Inconsistent Premium Plan payment behavior between Web and App</t>
+  </si>
+  <si>
+    <t>Bug-168</t>
+  </si>
+  <si>
+    <t>Add Pull-to-Refresh functionality on the Wallet screen</t>
+  </si>
+  <si>
+    <t>Bug-169</t>
+  </si>
+  <si>
+    <t>Previous dates should be disabled in the Delivery Date picker</t>
+  </si>
+  <si>
+    <t>Bug-170</t>
+  </si>
+  <si>
+    <t>Bug-171</t>
+  </si>
+  <si>
+    <t>Long product description breaks the UI</t>
+  </si>
+  <si>
+    <t>Bug-172</t>
+  </si>
+  <si>
+    <t>Create Product button width is too large</t>
+  </si>
+  <si>
+    <t>Bug-173</t>
+  </si>
+  <si>
+    <t>Confirm Delivery button is displayed before the final delivery step</t>
+  </si>
+  <si>
+    <t>Bug-174</t>
+  </si>
+  <si>
+    <t>Back button does not work after purchasing a Prestige product</t>
+  </si>
+  <si>
+    <t>Bug-175</t>
+  </si>
+  <si>
+    <t>Disable the "+" button when the maximum product quantity is reached</t>
+  </si>
+  <si>
+    <t>Bug-176</t>
+  </si>
+  <si>
+    <t>Incorrect confirmation message is displayed when Admin marks an order as Delivered</t>
+  </si>
+  <si>
+    <t>Bug-177</t>
+  </si>
+  <si>
+    <t>Waiting Approval status color is incorrect on the My Orders screen</t>
+  </si>
+  <si>
+    <t>Bug-178</t>
+  </si>
+  <si>
+    <t>Delivery Information should be empty when opening the Checkout screen</t>
+  </si>
+  <si>
+    <t>Bug-179</t>
+  </si>
+  <si>
+    <t>Keyboard covers the Delivery Instructions field</t>
+  </si>
+  <si>
+    <t>Bug-180</t>
+  </si>
+  <si>
+    <t>RBG balance overflows outside the Wallet text box</t>
+  </si>
+  <si>
+    <t>Bug-181</t>
+  </si>
+  <si>
+    <t>Available Balance and Insufficient Balance states are missing in P2P Transfer</t>
+  </si>
+  <si>
+    <t>Bug-182</t>
+  </si>
+  <si>
+    <t>Back navigation from Conversion Success/Failed screen is incorrect</t>
+  </si>
+  <si>
+    <t>Bug-183</t>
+  </si>
+  <si>
+    <t>Amount calculations are not displayed without entering a Wallet ID in P2P Transfer</t>
+  </si>
+  <si>
+    <t>Bug-184</t>
+  </si>
+  <si>
+    <t>Exit confirmation dialog is missing when leaving P2P Transfer with unsaved data</t>
+  </si>
+  <si>
+    <t>Bug-185</t>
+  </si>
+  <si>
+    <t>Calculated values should be cleared when the Amount field is empty in P2P Transfer</t>
+  </si>
+  <si>
+    <t>Bug-186</t>
+  </si>
+  <si>
+    <t>Amount field should allow a maximum of 8 digits in P2P Transfer</t>
+  </si>
+  <si>
+    <t>Bug-187</t>
+  </si>
+  <si>
+    <t>Incorrect text color for Amount and Category on the Cart screen</t>
+  </si>
+  <si>
+    <t>Bug-188</t>
+  </si>
+  <si>
+    <t>Input field remains focused after keyboard is dismissed</t>
+  </si>
+  <si>
+    <t>Bug-189</t>
+  </si>
+  <si>
+    <t>Keyboard should dismiss when tapping outside the input field</t>
+  </si>
+  <si>
+    <t>Bug-190</t>
+  </si>
+  <si>
+    <t>Wallet balance should not display unnecessary decimal places for zero RBF</t>
+  </si>
+  <si>
+    <t>Bug-191</t>
+  </si>
+  <si>
+    <t>Conversion Failed screen is missing</t>
+  </si>
+  <si>
+    <t>Bug-192</t>
+  </si>
+  <si>
+    <t>Incorrect RBF conversion rate is displayed</t>
+  </si>
+  <si>
+    <t>Bug-193</t>
+  </si>
+  <si>
+    <t>Conversion screen displays incomplete text</t>
+  </si>
+  <si>
+    <t>Bug-194</t>
+  </si>
+  <si>
+    <t>Conversion values should reset when switching units in RBF/RBG Conversion</t>
+  </si>
+  <si>
+    <t>Bug-195</t>
+  </si>
+  <si>
+    <t>Add a clear (✕) button to the Date filter on the Transactions screen</t>
+  </si>
+  <si>
+    <t>Bug-196</t>
+  </si>
+  <si>
+    <t>Time is missing in Pack Purchase transaction details</t>
+  </si>
+  <si>
+    <t>Bug-197</t>
+  </si>
+  <si>
+    <t>Amount is displayed with unnecessary trailing zero</t>
+  </si>
+  <si>
+    <t>Bug-198</t>
+  </si>
+  <si>
+    <t>Duration is missing in Pack transaction details</t>
+  </si>
+  <si>
+    <t>Bug-199</t>
+  </si>
+  <si>
+    <t>Do not display decimal places when the value has no decimal fraction (transaction)</t>
+  </si>
+  <si>
+    <t>Bug-200</t>
+  </si>
+  <si>
+    <t>Recent Transactions bottom sheet does not open in Wallet</t>
+  </si>
+  <si>
+    <t>Bug-201</t>
+  </si>
+  <si>
+    <t>Incorrect validation message is displayed for the Review Message field</t>
+  </si>
+  <si>
+    <t>Bug-202</t>
+  </si>
+  <si>
+    <t>View all text should be displayed in lowercase on the Products screen</t>
+  </si>
+  <si>
+    <t>Bug-203</t>
+  </si>
+  <si>
+    <t>Review Title and Message validations are missing</t>
+  </si>
+  <si>
+    <t>Bug-204</t>
+  </si>
+  <si>
+    <t>Scrolling is not working on the Product Listing screen (filter)</t>
+  </si>
+  <si>
+    <t>Bug-205</t>
+  </si>
+  <si>
+    <t>Item name should use initial capitalization</t>
+  </si>
+  <si>
+    <t>Bug-206</t>
+  </si>
+  <si>
+    <t>End Date should be removed from P2P Transfer Received</t>
+  </si>
+  <si>
+    <t>Bug-207</t>
+  </si>
+  <si>
+    <t>Verification tick should not be displayed for users without KYC</t>
+  </si>
+  <si>
+    <t>Bug-208</t>
+  </si>
+  <si>
+    <t>View All navigates to Category instead of Product Listing</t>
+  </si>
+  <si>
+    <t>Bug-209</t>
+  </si>
+  <si>
+    <t>New user registration fails with server error</t>
+  </si>
+  <si>
+    <t>Bug-210</t>
+  </si>
+  <si>
+    <t>First Name and Last Name field validation does not work correctly for maximum character limit</t>
+  </si>
+  <si>
+    <t>Bug-211</t>
+  </si>
+  <si>
+    <t>User is automatically logged out after 10 minutes</t>
+  </si>
+  <si>
+    <t>Bug-212</t>
+  </si>
+  <si>
+    <t>Withdrawal screen button does not match the approved design</t>
+  </si>
+  <si>
+    <t>Bug-213</t>
+  </si>
+  <si>
+    <t>No Result Found message is not center-aligned on the Support screen</t>
+  </si>
+  <si>
+    <t>Bug-214</t>
+  </si>
+  <si>
+    <t>Transaction filter bottom sheet spacing issue</t>
+  </si>
+  <si>
+    <t>Bug-215</t>
+  </si>
+  <si>
+    <t>Price filter size is incorrect on the Product Listing screen</t>
+  </si>
+  <si>
+    <t>Bug-216</t>
+  </si>
+  <si>
+    <t>Reviewer name initials are not capitalized</t>
+  </si>
+  <si>
+    <t>Bug-217</t>
+  </si>
+  <si>
+    <t>RBF screen does not load correctly and Cart icon is displayed during loading</t>
+  </si>
+  <si>
+    <t>Bug-218</t>
+  </si>
+  <si>
+    <t>Incorrect spelling of "P2P Transfer" in Wallet</t>
+  </si>
+  <si>
+    <t>Bug-219</t>
+  </si>
+  <si>
+    <t>RBF Packs are displayed in the incorrect order and tile colors do not match the design</t>
+  </si>
+  <si>
+    <t>Bug-220</t>
+  </si>
+  <si>
+    <t>Incorrect minimum and maximum limits configured for the 50,000 RBF Pack</t>
+  </si>
+  <si>
+    <t>Bug-221</t>
+  </si>
+  <si>
+    <t>Number field does not accept input while purchasing an RBF Service Pack</t>
+  </si>
+  <si>
+    <t>Bug-222</t>
+  </si>
+  <si>
+    <t>Newly created user is assigned 0 RBF</t>
+  </si>
+  <si>
+    <t>Bug-223</t>
+  </si>
+  <si>
+    <t>New user creation fails with "Unauthorized" error</t>
+  </si>
+  <si>
+    <t>Bug-224</t>
+  </si>
+  <si>
+    <t>Plus (+) sign is missing with Service Pack amount</t>
+  </si>
+  <si>
+    <t>Bug-225</t>
+  </si>
+  <si>
+    <t>Login form data is not cleared after registering a new account and logging out</t>
+  </si>
+  <si>
+    <t>Bug-226</t>
+  </si>
+  <si>
+    <t>Incorrect spelling of "Packs" on Total Weekly Earnings card. Dashboard</t>
+  </si>
+  <si>
+    <t>Bug-227</t>
+  </si>
+  <si>
+    <t>Incorrect validation message is displayed for invalid OTP</t>
+  </si>
+  <si>
+    <t>Bug-228</t>
+  </si>
+  <si>
+    <t>First Name and Last Name fields should use initial capital keyboard</t>
+  </si>
+  <si>
+    <t>Bug-229</t>
+  </si>
+  <si>
+    <t>Unable to sign up due to incorrect internet connection error</t>
+  </si>
+  <si>
+    <t>Bug-230</t>
+  </si>
+  <si>
+    <t>Keyboard hides text fields on authentication screens</t>
+  </si>
+  <si>
+    <t>Bug-231</t>
+  </si>
+  <si>
+    <t>Onboarding screens are missing</t>
+  </si>
+  <si>
+    <t>Bug-232</t>
+  </si>
+  <si>
+    <t>Support list table is not displayed in Mobile Responsive view</t>
+  </si>
+  <si>
+    <t>Bug-233</t>
+  </si>
+  <si>
+    <t>Filter control size changes after selecting an option in Mobile Responsive view</t>
+  </si>
+  <si>
+    <t>Bug-234</t>
+  </si>
+  <si>
+    <t>Search box height does not match the approved design in Mobile Responsive view</t>
+  </si>
+  <si>
+    <t>Bug-235</t>
+  </si>
+  <si>
+    <t>Text field zooms in when focused in Mobile Responsive view</t>
+  </si>
+  <si>
+    <t>Bug-236</t>
+  </si>
+  <si>
+    <t>Admin notes are not visible to the user</t>
+  </si>
+  <si>
+    <t>Bug-237</t>
+  </si>
+  <si>
+    <t>Admin should not add notes multiple times on a support ticket</t>
+  </si>
+  <si>
+    <t>Bug-238</t>
+  </si>
+  <si>
+    <t>RBF Logs display receiver transaction history before sender transaction history</t>
+  </si>
+  <si>
+    <t>Bug-239</t>
+  </si>
+  <si>
+    <t>No actions should be allowed after a ticket is resolved</t>
+  </si>
+  <si>
+    <t>Bug-240</t>
+  </si>
+  <si>
+    <t>Incorrect transaction type is displayed in RBF Supply when purchasing a Service Pack</t>
+  </si>
+  <si>
+    <t>Bug-241</t>
+  </si>
+  <si>
+    <t>PDF export does not handle long data correctly</t>
+  </si>
+  <si>
+    <t>Bug-242</t>
+  </si>
+  <si>
+    <t>Text alignment is incorrect on Product Details and cart screen</t>
+  </si>
+  <si>
+    <t>Bug-243</t>
+  </si>
+  <si>
+    <t>Incorrect Product status values are displayed</t>
+  </si>
+  <si>
+    <t>Bug-244</t>
+  </si>
+  <si>
+    <t>Partner login flow should require email registration before password reset</t>
+  </si>
+  <si>
+    <t>Bug-245</t>
+  </si>
+  <si>
+    <t>Sub Category Edit modal does not display long data correctly</t>
+  </si>
+  <si>
+    <t>Bug-246</t>
+  </si>
+  <si>
+    <t>Long Category Title should be truncated with ellipsis</t>
+  </si>
+  <si>
+    <t>Bug-247</t>
+  </si>
+  <si>
+    <t>Category Title field should enforce a maximum limit of 150 characters</t>
+  </si>
+  <si>
+    <t>Bug-248</t>
+  </si>
+  <si>
+    <t>Volume is not displayed on Product Details screen in Admin Panel</t>
+  </si>
+  <si>
+    <t>Bug-249</t>
+  </si>
+  <si>
+    <t>Incorrect validation message is displayed when entering letters in Amount and Volume fields</t>
+  </si>
+  <si>
+    <t>Bug-250</t>
+  </si>
+  <si>
+    <t>Incorrect validation error is displayed when selecting Approved or Rejected filters on Products screen</t>
+  </si>
+  <si>
+    <t>Bug-251</t>
+  </si>
+  <si>
+    <t>Product cards are missing on the Product screen</t>
+  </si>
+  <si>
+    <t>Bug-252</t>
+  </si>
+  <si>
+    <t>Newly added Categories and Sub Categories should appear at the top of the list</t>
+  </si>
+  <si>
+    <t>Bug-253</t>
+  </si>
+  <si>
+    <t>Product amount should be displayed in Dollars instead of RBG (partner product)</t>
+  </si>
+  <si>
+    <t>Bug-254</t>
+  </si>
+  <si>
+    <t>Incorrect actions are displayed on the View Sub Category screen</t>
+  </si>
+  <si>
+    <t>Bug-255</t>
+  </si>
+  <si>
+    <t>Partner should not be able to log in when status is Pending or Suspended</t>
+  </si>
+  <si>
+    <t>Bug-256</t>
+  </si>
+  <si>
+    <t>Partner is unable to log in due to invalid OTP error</t>
+  </si>
+  <si>
+    <t>Bug-257</t>
+  </si>
+  <si>
+    <t>Scrolling is not working on the Create Partner screen</t>
+  </si>
+  <si>
+    <t>Bug-258</t>
+  </si>
+  <si>
+    <t>Incorrect page size/layout in Users PDF export</t>
+  </si>
+  <si>
+    <t>Bug-259</t>
+  </si>
+  <si>
+    <t>Incorrect export time displayed in Users PDF</t>
+  </si>
+  <si>
+    <t>Bug-260</t>
+  </si>
+  <si>
+    <t>Export Report functionality is not working</t>
+  </si>
+  <si>
+    <t>Bug-261</t>
+  </si>
+  <si>
+    <t>KYC search does not work with user's full name</t>
+  </si>
+  <si>
+    <t>Bug-262</t>
+  </si>
+  <si>
+    <t>Data is cleared when changing page size limit</t>
+  </si>
+  <si>
+    <t>Bug-263</t>
+  </si>
+  <si>
+    <t>Incorrect toast message is displayed when changing Pack status</t>
+  </si>
+  <si>
+    <t>Bug-264</t>
+  </si>
+  <si>
+    <t>Number counter should be removed from Royalty Points field</t>
+  </si>
+  <si>
+    <t>Bug-265</t>
+  </si>
+  <si>
+    <t>Service Pack values should display only two decimal places</t>
+  </si>
+  <si>
+    <t>Bug-266</t>
+  </si>
+  <si>
+    <t>Landing page -- Responsive issue</t>
+  </si>
+  <si>
+    <t>Bug-267</t>
+  </si>
+  <si>
+    <t>Landing page -- Mobile responsive – email input causes zoom and keyboard behavior issue</t>
+  </si>
+  <si>
+    <t>Bug-268</t>
+  </si>
+  <si>
+    <t>Landing page -- Favicon is missing from the application</t>
+  </si>
+  <si>
+    <t>Bug-269</t>
+  </si>
+  <si>
+    <t>Landing page -- Social media icons incorrectly navigate to top of the page</t>
+  </si>
+  <si>
+    <t>Bug-270</t>
+  </si>
+  <si>
+    <t>Landing page -- Join Waitlist link is missing in Privacy Policy and Terms &amp; Conditions</t>
+  </si>
+  <si>
+    <t>Bug-271</t>
+  </si>
+  <si>
+    <t>Landing page -- Web layout missing left and right padding</t>
+  </si>
+  <si>
+    <t>Bug-272</t>
+  </si>
+  <si>
+    <t>Landing page -- Email placeholder is not fully displayed</t>
+  </si>
+  <si>
+    <t>Bug-273</t>
+  </si>
+  <si>
+    <t>Landing page -- Logo does not have a clickable link</t>
+  </si>
+  <si>
+    <t>Bug-274</t>
+  </si>
+  <si>
+    <t>Landing page -- RBF Marketplace image position does not match the approved design</t>
+  </si>
+  <si>
+    <t>Bug-275</t>
+  </si>
+  <si>
+    <t>Landing page -- Background color does not match the approved design</t>
+  </si>
+  <si>
+    <t>Bug-276</t>
+  </si>
+  <si>
+    <t>Landing page -- Email text box color does not match the approved design</t>
+  </si>
+  <si>
+    <t>Bug-277</t>
+  </si>
+  <si>
+    <t>Landing page -- Email text is truncated in banner due to insufficient container size</t>
+  </si>
+  <si>
+    <t>Bug-278</t>
+  </si>
+  <si>
+    <t>Royal Flow Control screen does not match the approved design</t>
+  </si>
+  <si>
+    <t>Bug-279</t>
+  </si>
+  <si>
+    <t>Royal Movements Log screen does not match the approved design</t>
+  </si>
+  <si>
+    <t>Bug-280</t>
+  </si>
+  <si>
+    <t>Add Notes modal in Support Details does not match the approved design</t>
+  </si>
+  <si>
+    <t>Bug-281</t>
+  </si>
+  <si>
+    <t>Support Detail screen does not match the approved design</t>
+  </si>
+  <si>
+    <t>Bug-282</t>
+  </si>
+  <si>
+    <t>Support – Actions UI does not match the approved design</t>
+  </si>
+  <si>
+    <t>Bug-283</t>
+  </si>
+  <si>
+    <t>Support – Status colors do not match the approved design</t>
+  </si>
+  <si>
+    <t>Bug-284</t>
+  </si>
+  <si>
+    <t>KYC rejected toast message does not match design</t>
+  </si>
+  <si>
+    <t>Bug-285</t>
+  </si>
+  <si>
+    <t>Reject This KYC popup does not match the design</t>
+  </si>
+  <si>
+    <t>Bug-286</t>
+  </si>
+  <si>
+    <t>KYC status does not match the approved design</t>
+  </si>
+  <si>
+    <t>Bug-287</t>
+  </si>
+  <si>
+    <t>Withdrawal Approval user avatars do not match design</t>
+  </si>
+  <si>
+    <t>Bug-288</t>
+  </si>
+  <si>
+    <t>Module screens do not open from the top of the page</t>
+  </si>
+  <si>
+    <t>Bug-289</t>
+  </si>
+  <si>
+    <t>Suspend User toast message icon does not match design</t>
+  </si>
+  <si>
+    <t>Bug-290</t>
+  </si>
+  <si>
+    <t>Users dropdown contains duplicate Users menu item</t>
+  </si>
+  <si>
+    <t>Bug-291</t>
+  </si>
+  <si>
+    <t>Cancel button border color is incorrect in delete confirmation popup</t>
+  </si>
+  <si>
+    <t>Bug-292</t>
+  </si>
+  <si>
+    <t>Action buttons do not match approved UI design</t>
+  </si>
+  <si>
+    <t>Bug-293</t>
+  </si>
+  <si>
+    <t>Label displays unwanted space between asterisk (*) and text</t>
+  </si>
+  <si>
+    <t>Bug-294</t>
+  </si>
+  <si>
+    <t>Values do not update when changing conversion type</t>
+  </si>
+  <si>
+    <t>Bug-295</t>
+  </si>
+  <si>
+    <t>Verify Your Identity – Submit for Review button state does not match design</t>
+  </si>
+  <si>
+    <t>Bug-296</t>
+  </si>
+  <si>
+    <t>Verify Your Identity – Scroll is missing</t>
+  </si>
+  <si>
+    <t>Bug-297</t>
+  </si>
+  <si>
+    <t>Verify Your Identity – Tick position is incorrect under images</t>
+  </si>
+  <si>
+    <t>Bug-298</t>
+  </si>
+  <si>
+    <t>Verify Your Identity – Image shadow appears incorrectly</t>
+  </si>
+  <si>
+    <t>Bug-299</t>
+  </si>
+  <si>
+    <t>Verify Your Identity – National ID and Passport icon boxes mismatch design</t>
+  </si>
+  <si>
+    <t>Bug-300</t>
+  </si>
+  <si>
+    <t>FAQ arrow icon size mismatch</t>
+  </si>
+  <si>
+    <t>Bug-301</t>
+  </si>
+  <si>
+    <t>FAQ screen padding issue</t>
+  </si>
+  <si>
+    <t>Bug-302</t>
+  </si>
+  <si>
+    <t>Email field should be disabled in Edit Profile</t>
+  </si>
+  <si>
+    <t>Bug-303</t>
+  </si>
+  <si>
+    <t>Submit button design mismatch in product details</t>
+  </si>
+  <si>
+    <t>Bug-304</t>
+  </si>
+  <si>
+    <t>See all reviews button design mismatch</t>
+  </si>
+  <si>
+    <t>Bug-305</t>
+  </si>
+  <si>
+    <t>Product quantity minus button not disabled at 1</t>
+  </si>
+  <si>
+    <t>Bug-306</t>
+  </si>
+  <si>
+    <t>Product filter bottom sheet spacing issue</t>
+  </si>
+  <si>
+    <t>Bug-307</t>
+  </si>
+  <si>
+    <t>Product price unit color mismatch</t>
+  </si>
+  <si>
+    <t>Bug-308</t>
+  </si>
+  <si>
+    <t>Radio button design mismatch in filters</t>
+  </si>
+  <si>
+    <t>Bug-309</t>
+  </si>
+  <si>
+    <t>Product listing search bar design mismatch</t>
+  </si>
+  <si>
+    <t>Bug-310</t>
+  </si>
+  <si>
+    <t>My Orders filter bottom sheet spacing issue</t>
+  </si>
+  <si>
+    <t>Bug-311</t>
+  </si>
+  <si>
+    <t>My Orders search bar design mismatch</t>
+  </si>
+  <si>
+    <t>Bug-312</t>
+  </si>
+  <si>
+    <t>Support filter tick icon pixel issue</t>
+  </si>
+  <si>
+    <t>Bug-313</t>
+  </si>
+  <si>
+    <t>Support filter bottom sheet spacing issue</t>
+  </si>
+  <si>
+    <t>Bug-314</t>
+  </si>
+  <si>
+    <t>Add icon should not shown in bottom area when Create Ticket is enabled.</t>
+  </si>
+  <si>
+    <t>Bug-315</t>
+  </si>
+  <si>
+    <t>Create Ticket button hides search and filter</t>
+  </si>
+  <si>
+    <t>Bug-316</t>
+  </si>
+  <si>
+    <t>Support search bar design mismatch</t>
+  </si>
+  <si>
+    <t>Bug-317</t>
+  </si>
+  <si>
+    <t>My Referrals levels positioning incorrect</t>
+  </si>
+  <si>
+    <t>Bug-318</t>
+  </si>
+  <si>
+    <t>Refer &amp; Earn sliders misaligned</t>
+  </si>
+  <si>
+    <t>Bug-319</t>
+  </si>
+  <si>
+    <t>Bonus level card size too large</t>
+  </si>
+  <si>
+    <t>Bug-320</t>
+  </si>
+  <si>
+    <t>Refer &amp; Earn heading missing Bonus level label</t>
+  </si>
+  <si>
+    <t>Bug-321</t>
+  </si>
+  <si>
+    <t>Arrow icons size mismatch in More screen</t>
+  </si>
+  <si>
+    <t>Bug-322</t>
+  </si>
+  <si>
+    <t>More screen padding missing</t>
+  </si>
+  <si>
+    <t>Bug-323</t>
+  </si>
+  <si>
+    <t>Filter "Clear All" text casing incorrect</t>
+  </si>
+  <si>
+    <t>Bug-324</t>
+  </si>
+  <si>
+    <t>Incorrect label "withdrawal" instead of "withdrawals"</t>
+  </si>
+  <si>
+    <t>Bug-325</t>
+  </si>
+  <si>
+    <t>Transaction search bar design mismatch (text color)</t>
+  </si>
+  <si>
+    <t>Bug-326</t>
+  </si>
+  <si>
+    <t>Transaction search and filter field size mismatch</t>
+  </si>
+  <si>
+    <t>Bug-327</t>
+  </si>
+  <si>
+    <t>Transaction filter text color mismatch</t>
+  </si>
+  <si>
+    <t>Bug-328</t>
+  </si>
+  <si>
+    <t>Wallet card text color mismatch</t>
+  </si>
+  <si>
+    <t>Bug-329</t>
+  </si>
+  <si>
+    <t>Empty state missing View All in recent transactions</t>
+  </si>
+  <si>
+    <t>Bug-330</t>
+  </si>
+  <si>
+    <t>Withdraw button color mismatch in wallet</t>
+  </si>
+  <si>
+    <t>Bug-331</t>
+  </si>
+  <si>
+    <t>Wallet sliders misaligned</t>
+  </si>
+  <si>
+    <t>Bug-332</t>
+  </si>
+  <si>
+    <t>Navigation bar icons mismatch design</t>
+  </si>
+  <si>
+    <t>Bug-333</t>
+  </si>
+  <si>
+    <t>RBF confirmation screen missing</t>
+  </si>
+  <si>
+    <t>Bug-334</t>
+  </si>
+  <si>
+    <t>Connect Wallet button misaligned in bottom sheet</t>
+  </si>
+  <si>
+    <t>Bug-335</t>
+  </si>
+  <si>
+    <t>RBF service pack color mismatch</t>
+  </si>
+  <si>
+    <t>Bug-336</t>
+  </si>
+  <si>
+    <t>All Packs screen missing scroll</t>
+  </si>
+  <si>
+    <t>Bug-337</t>
+  </si>
+  <si>
+    <t>View All Packs text too small on dashboard</t>
+  </si>
+  <si>
+    <t>Bug-338</t>
+  </si>
+  <si>
+    <t>Font inconsistency across app</t>
+  </si>
+  <si>
+    <t>Bug-339</t>
+  </si>
+  <si>
+    <t>Dashboard sliders partially visible</t>
+  </si>
+  <si>
+    <t>Bug-340</t>
+  </si>
+  <si>
+    <t>Bottom navigation bar not fully visible</t>
+  </si>
+  <si>
+    <t>Bug-341</t>
+  </si>
+  <si>
+    <t>KYC screens missing</t>
+  </si>
+  <si>
+    <t>Bug-342</t>
+  </si>
+  <si>
+    <t>Verify Your Identity – Box size does not match design</t>
+  </si>
+  <si>
+    <t>Bug-343</t>
+  </si>
+  <si>
+    <t>Buttons and text misaligned at screen bottom</t>
+  </si>
+  <si>
+    <t>Bug-344</t>
+  </si>
+  <si>
+    <t>Do this later text capitalization issue</t>
+  </si>
+  <si>
+    <t>Bug-345</t>
+  </si>
+  <si>
+    <t>Email verification heading capitalization issue</t>
+  </si>
+  <si>
+    <t>Bug-346</t>
+  </si>
+  <si>
+    <t>Password eye icon does not match design</t>
+  </si>
+  <si>
+    <t>Bug-347</t>
+  </si>
+  <si>
+    <t>I am agree text incorrect on sign up screen</t>
+  </si>
+  <si>
+    <t>Bug-348</t>
+  </si>
+  <si>
+    <t>Keyboard overlaps text field</t>
+  </si>
+  <si>
+    <t>Bug-349</t>
+  </si>
+  <si>
+    <t>Validation error message is truncated</t>
+  </si>
+  <si>
+    <t>Bug-350</t>
+  </si>
+  <si>
+    <t>Validation error causes text field UI shift</t>
+  </si>
+  <si>
+    <t>Bug-351</t>
+  </si>
+  <si>
+    <t>Sign up heading font mismatch</t>
+  </si>
+  <si>
+    <t>Bug-352</t>
+  </si>
+  <si>
+    <t>Placeholder color mismatch in text fields</t>
+  </si>
+  <si>
+    <t>Bug-353</t>
+  </si>
+  <si>
+    <t>Terms &amp; Conditions and Privacy Policy links not clickable</t>
+  </si>
+  <si>
+    <t>Bug-354</t>
+  </si>
+  <si>
+    <t>Onboarding reappears after back navigation from Create Account/Login</t>
+  </si>
+  <si>
+    <t>Bug-355</t>
+  </si>
+  <si>
+    <t>Packages image mismatch on onboarding 2nd screen</t>
+  </si>
+  <si>
+    <t>Bug-356</t>
+  </si>
+  <si>
+    <t>Font size issue on onboarding screen</t>
+  </si>
+  <si>
+    <t>Bug-357</t>
+  </si>
+  <si>
+    <t>Login button color mismatch on onboarding screen</t>
+  </si>
+  <si>
+    <t>Bug-358</t>
+  </si>
+  <si>
+    <t>Conversion values between 1 and 1.9 are not displayed correctly</t>
+  </si>
+  <si>
+    <t>Bug-359</t>
+  </si>
+  <si>
     <t>Remove Plus Sign from Platinum Service Pack</t>
   </si>
   <si>
-    <t>Bug-120</t>
+    <t>Bug-360</t>
   </si>
   <si>
     <t>Automatic referral code</t>
   </si>
   <si>
-    <t>Bug-121</t>
+    <t>Bug-361</t>
   </si>
   <si>
     <t>Remove Physical Gold message from Add to Cart.</t>
   </si>
   <si>
-    <t>Bug-122</t>
+    <t>Bug-362</t>
   </si>
   <si>
     <t>On the mobile responsive landing page, the drawer displays “Welcome to Royal” instead of the correct name.</t>
   </si>
   <si>
-    <t>Bug-123</t>
+    <t>Bug-363</t>
   </si>
   <si>
     <t>On mobile responsive view, there is an issue when attempting to close the Drawer or Notification Modal.</t>
   </si>
   <si>
-    <t>Bug-124</t>
+    <t>Bug-364</t>
   </si>
   <si>
     <t>The alignment of the Tier Levels section is not correct.</t>
   </si>
   <si>
-    <t>Bug-125</t>
+    <t>Bug-365</t>
   </si>
   <si>
     <t>Incorrect session data is displayed.</t>
   </si>
   <si>
-    <t>Bug-126</t>
+    <t>Bug-366</t>
   </si>
   <si>
     <t>Mobile Responsive ---- reset password</t>
   </si>
   <si>
-    <t>Bug-127</t>
+    <t>Bug-367</t>
   </si>
   <si>
     <t>Mobile Responsive --- OTP screen</t>
   </si>
   <si>
-    <t>Bug-128</t>
+    <t>Bug-368</t>
   </si>
   <si>
     <t>Mobile Responsive ---- TRC20</t>
   </si>
   <si>
-    <t>Bug-129</t>
+    <t>Bug-369</t>
   </si>
   <si>
     <t>Mobile Responsive ---- withdrawal</t>
   </si>
   <si>
-    <t>Bug-130</t>
+    <t>Bug-370</t>
   </si>
   <si>
     <t>Remove Conversion Fee from Sell Gold Details</t>
   </si>
   <si>
-    <t>Bug-131</t>
+    <t>Bug-371</t>
   </si>
   <si>
     <t>Mobile Responsive ---- all packs</t>
   </si>
   <si>
-    <t>Bug-132</t>
+    <t>Bug-372</t>
   </si>
   <si>
     <t>Incorrect Android Version Displayed for Chrome Browser Session</t>
   </si>
   <si>
-    <t>Bug-133</t>
+    <t>Bug-373</t>
   </si>
   <si>
     <t>The user's session remains marked as Active in the Active Sessions section even after the user has logged out.</t>
   </si>
   <si>
-    <t>Bug-134</t>
-  </si>
-  <si>
-    <t>Remove the "Cancelled" status from the My Orders screen</t>
-  </si>
-  <si>
-    <t>Bug-135</t>
-  </si>
-  <si>
-    <t>Bug-136</t>
-  </si>
-  <si>
-    <t>Add bottom spacing on the Product Listing screen</t>
-  </si>
-  <si>
-    <t>Bug-137</t>
-  </si>
-  <si>
-    <t>Prevent adding more than the available product quantity</t>
-  </si>
-  <si>
-    <t>Bug-138</t>
-  </si>
-  <si>
-    <t>Product Details should display the default quantity and "Add to Cart" button when the cart quantity is below the maximum</t>
-  </si>
-  <si>
-    <t>Bug-139</t>
-  </si>
-  <si>
-    <t>Allow manual entry of item quantity</t>
-  </si>
-  <si>
-    <t>Bug-140</t>
-  </si>
-  <si>
-    <t>RBF balance should not be abbreviated in millions or billions</t>
-  </si>
-  <si>
-    <t>Bug-141</t>
-  </si>
-  <si>
-    <t>Display RBG amounts in grams (g) in the Wallet</t>
-  </si>
-  <si>
-    <t>Bug-142</t>
-  </si>
-  <si>
-    <t>Display a "Sort By" option before selecting a sorting method</t>
-  </si>
-  <si>
-    <t>Bug-143</t>
-  </si>
-  <si>
-    <t>Add additional sorting options to the Product filter</t>
-  </si>
-  <si>
-    <t>Bug-144</t>
-  </si>
-  <si>
-    <t>Oldest filter is not working on the Product Listing screen</t>
-  </si>
-  <si>
-    <t>Bug-145</t>
-  </si>
-  <si>
-    <t>Bug-146</t>
-  </si>
-  <si>
-    <t>Bug-147</t>
-  </si>
-  <si>
-    <t>Display the correct currency based on the product type</t>
-  </si>
-  <si>
-    <t>Bug-148</t>
-  </si>
-  <si>
-    <t>Replace USDT with RBF and RBG in the Product filter</t>
-  </si>
-  <si>
-    <t>Bug-149</t>
-  </si>
-  <si>
-    <t>Bug-150</t>
-  </si>
-  <si>
-    <t>Default price range should be 0–1000 in the Product filter</t>
-  </si>
-  <si>
-    <t>Bug-151</t>
-  </si>
-  <si>
-    <t>Bug-152</t>
-  </si>
-  <si>
-    <t>Do not display a separate Transaction ID for Conversion transactions</t>
-  </si>
-  <si>
-    <t>Bug-153</t>
-  </si>
-  <si>
-    <t>RBF RBG label is missing on the Conversion</t>
-  </si>
-  <si>
-    <t>Bug-154</t>
-  </si>
-  <si>
-    <t>User should remain logged in when navigating from Change Password to Forgot Password</t>
-  </si>
-  <si>
-    <t>Bug-155</t>
-  </si>
-  <si>
-    <t>Pre-fill email on the Forgot Password screen when navigated from Change Password</t>
-  </si>
-  <si>
-    <t>Bug-156</t>
-  </si>
-  <si>
-    <t>When navigating from the Change Password screen to the Forgot Password screen, the user's email address is pre-filled but remains editable.</t>
-  </si>
-  <si>
-    <t>Bug-157</t>
-  </si>
-  <si>
-    <t>KYC record order changes after approval or rejection by Admin</t>
-  </si>
-  <si>
-    <t>Bug-158</t>
-  </si>
-  <si>
-    <t>Long filter text breaks the UI on the Product Listing screen</t>
-  </si>
-  <si>
-    <t>Bug-159</t>
-  </si>
-  <si>
-    <t>KYC file upload accepts files larger than 5 MB</t>
-  </si>
-  <si>
-    <t>Bug-160</t>
-  </si>
-  <si>
-    <t>Add Pull-to-Refresh functionality on the KYC Details screen</t>
-  </si>
-  <si>
-    <t>Bug-161</t>
-  </si>
-  <si>
-    <t>Rejected reason is not displayed after KYC rejection</t>
-  </si>
-  <si>
-    <t>Bug-162</t>
-  </si>
-  <si>
-    <t>KYC image dimensions are incorrect on the KYC Details screen --- admin</t>
-  </si>
-  <si>
-    <t>Bug-163</t>
-  </si>
-  <si>
-    <t>KYC status should display "Pending"</t>
-  </si>
-  <si>
-    <t>Bug-164</t>
-  </si>
-  <si>
-    <t>ID should be displayed in uppercase on the KYC Details screen</t>
-  </si>
-  <si>
-    <t>Bug-165</t>
-  </si>
-  <si>
-    <t>P2P Transfer screen becomes unresponsive after navigating back</t>
-  </si>
-  <si>
-    <t>Bug-166</t>
-  </si>
-  <si>
-    <t>Incorrect initial error message is displayed on the P2P Transfer screen</t>
-  </si>
-  <si>
-    <t>Bug-167</t>
-  </si>
-  <si>
-    <t>Incorrect button text on the P2P Transfer Failed screen</t>
-  </si>
-  <si>
-    <t>Bug-168</t>
-  </si>
-  <si>
-    <t>Keyboard overlaps the text field on the Review screen</t>
-  </si>
-  <si>
-    <t>Bug-169</t>
-  </si>
-  <si>
-    <t>Incorrect conversion rate displayed as "1 RBF = 0 RBG"</t>
-  </si>
-  <si>
-    <t>Bug-170</t>
-  </si>
-  <si>
-    <t>Edit Profile screen is missing field validations</t>
-  </si>
-  <si>
-    <t>Bug-171</t>
-  </si>
-  <si>
-    <t>Apply an 8-digit input limit to Amount fields in P2P Transfer and Service Pack</t>
-  </si>
-  <si>
-    <t>Bug-172</t>
-  </si>
-  <si>
-    <t>Bug-173</t>
-  </si>
-  <si>
-    <t>Bottom navigation bar disappears after changing the password</t>
-  </si>
-  <si>
-    <t>Bug-174</t>
-  </si>
-  <si>
-    <t>Verification tick should not displays on the KYC Details screen for approved KYC</t>
-  </si>
-  <si>
-    <t>Bug-175</t>
-  </si>
-  <si>
-    <t>Session expires on the Change Password screen</t>
-  </si>
-  <si>
-    <t>Bug-176</t>
-  </si>
-  <si>
-    <t>Delivery Date should not be displayed for Prestige orders</t>
-  </si>
-  <si>
-    <t>Bug-177</t>
-  </si>
-  <si>
-    <t>Delivery Date column should not be displayed in Order Management for the Partner flow</t>
-  </si>
-  <si>
-    <t>Bug-178</t>
-  </si>
-  <si>
-    <t>Long order details should be truncated with ellipsis in Prestige Marketplace</t>
-  </si>
-  <si>
-    <t>Bug-179</t>
-  </si>
-  <si>
-    <t>Incorrect order image is displayed temporarily on the My Orders screen</t>
-  </si>
-  <si>
-    <t>Bug-180</t>
-  </si>
-  <si>
-    <t>Web application crashes when entering long text in Meeting Place and Delivery Instructions</t>
-  </si>
-  <si>
-    <t>Bug-181</t>
-  </si>
-  <si>
-    <t>Long text breaks the UI in Meeting Place and Delivery Instructions fields</t>
-  </si>
-  <si>
-    <t>Bug-182</t>
-  </si>
-  <si>
-    <t>Inconsistent Premium Plan payment behavior between Web and App</t>
-  </si>
-  <si>
-    <t>Bug-183</t>
-  </si>
-  <si>
-    <t>Add Pull-to-Refresh functionality on the Wallet screen</t>
-  </si>
-  <si>
-    <t>Bug-184</t>
-  </si>
-  <si>
-    <t>Previous dates should be disabled in the Delivery Date picker</t>
-  </si>
-  <si>
-    <t>Bug-185</t>
-  </si>
-  <si>
-    <t>Bug-186</t>
-  </si>
-  <si>
-    <t>Long product description breaks the UI</t>
-  </si>
-  <si>
-    <t>Bug-187</t>
-  </si>
-  <si>
-    <t>Create Product button width is too large</t>
-  </si>
-  <si>
-    <t>Bug-188</t>
-  </si>
-  <si>
-    <t>Confirm Delivery button is displayed before the final delivery step</t>
-  </si>
-  <si>
-    <t>Bug-189</t>
-  </si>
-  <si>
-    <t>Back button does not work after purchasing a Prestige product</t>
-  </si>
-  <si>
-    <t>Bug-190</t>
-  </si>
-  <si>
-    <t>Disable the "+" button when the maximum product quantity is reached</t>
-  </si>
-  <si>
-    <t>Bug-191</t>
-  </si>
-  <si>
-    <t>Incorrect confirmation message is displayed when Admin marks an order as Delivered</t>
-  </si>
-  <si>
-    <t>Bug-192</t>
-  </si>
-  <si>
-    <t>Waiting Approval status color is incorrect on the My Orders screen</t>
-  </si>
-  <si>
-    <t>Bug-193</t>
-  </si>
-  <si>
-    <t>Delivery Information should be empty when opening the Checkout screen</t>
-  </si>
-  <si>
-    <t>Bug-194</t>
-  </si>
-  <si>
-    <t>Keyboard covers the Delivery Instructions field</t>
-  </si>
-  <si>
-    <t>Bug-195</t>
-  </si>
-  <si>
-    <t>RBG balance overflows outside the Wallet text box</t>
-  </si>
-  <si>
-    <t>Bug-196</t>
-  </si>
-  <si>
-    <t>Available Balance and Insufficient Balance states are missing in P2P Transfer</t>
-  </si>
-  <si>
-    <t>Bug-197</t>
-  </si>
-  <si>
-    <t>Back navigation from Conversion Success/Failed screen is incorrect</t>
-  </si>
-  <si>
-    <t>Bug-198</t>
-  </si>
-  <si>
-    <t>Amount calculations are not displayed without entering a Wallet ID in P2P Transfer</t>
-  </si>
-  <si>
-    <t>Bug-199</t>
-  </si>
-  <si>
-    <t>Exit confirmation dialog is missing when leaving P2P Transfer with unsaved data</t>
-  </si>
-  <si>
-    <t>Bug-200</t>
-  </si>
-  <si>
-    <t>Calculated values should be cleared when the Amount field is empty in P2P Transfer</t>
-  </si>
-  <si>
-    <t>Bug-201</t>
-  </si>
-  <si>
-    <t>Amount field should allow a maximum of 8 digits in P2P Transfer</t>
-  </si>
-  <si>
-    <t>Bug-202</t>
-  </si>
-  <si>
-    <t>Incorrect text color for Amount and Category on the Cart screen</t>
-  </si>
-  <si>
-    <t>Bug-203</t>
-  </si>
-  <si>
-    <t>Input field remains focused after keyboard is dismissed</t>
-  </si>
-  <si>
-    <t>Bug-204</t>
-  </si>
-  <si>
-    <t>Keyboard should dismiss when tapping outside the input field</t>
-  </si>
-  <si>
-    <t>Bug-205</t>
-  </si>
-  <si>
-    <t>Wallet balance should not display unnecessary decimal places for zero RBF</t>
-  </si>
-  <si>
-    <t>Bug-206</t>
-  </si>
-  <si>
-    <t>Conversion Failed screen is missing</t>
-  </si>
-  <si>
-    <t>Bug-207</t>
-  </si>
-  <si>
-    <t>Incorrect RBF conversion rate is displayed</t>
-  </si>
-  <si>
-    <t>Bug-208</t>
-  </si>
-  <si>
-    <t>Conversion screen displays incomplete text</t>
-  </si>
-  <si>
-    <t>Bug-209</t>
-  </si>
-  <si>
-    <t>Conversion values should reset when switching units in RBF/RBG Conversion</t>
-  </si>
-  <si>
-    <t>Bug-210</t>
-  </si>
-  <si>
-    <t>Add a clear (✕) button to the Date filter on the Transactions screen</t>
-  </si>
-  <si>
-    <t>Bug-211</t>
-  </si>
-  <si>
-    <t>Time is missing in Pack Purchase transaction details</t>
-  </si>
-  <si>
-    <t>Bug-212</t>
-  </si>
-  <si>
-    <t>Amount is displayed with unnecessary trailing zero</t>
-  </si>
-  <si>
-    <t>Bug-213</t>
-  </si>
-  <si>
-    <t>Duration is missing in Pack transaction details</t>
-  </si>
-  <si>
-    <t>Bug-214</t>
-  </si>
-  <si>
-    <t>Do not display decimal places when the value has no decimal fraction (transaction)</t>
-  </si>
-  <si>
-    <t>Bug-215</t>
-  </si>
-  <si>
-    <t>Recent Transactions bottom sheet does not open in Wallet</t>
-  </si>
-  <si>
-    <t>Bug-216</t>
-  </si>
-  <si>
-    <t>Incorrect validation message is displayed for the Review Message field</t>
-  </si>
-  <si>
-    <t>Bug-217</t>
-  </si>
-  <si>
-    <t>View all text should be displayed in lowercase on the Products screen</t>
-  </si>
-  <si>
-    <t>Bug-218</t>
-  </si>
-  <si>
-    <t>Review Title and Message validations are missing</t>
-  </si>
-  <si>
-    <t>Bug-219</t>
-  </si>
-  <si>
-    <t>Scrolling is not working on the Product Listing screen (filter)</t>
-  </si>
-  <si>
-    <t>Bug-220</t>
-  </si>
-  <si>
-    <t>Item name should use initial capitalization</t>
-  </si>
-  <si>
-    <t>Bug-221</t>
-  </si>
-  <si>
-    <t>End Date should be removed from P2P Transfer Received</t>
-  </si>
-  <si>
-    <t>Bug-222</t>
-  </si>
-  <si>
-    <t>Verification tick should not be displayed for users without KYC</t>
-  </si>
-  <si>
-    <t>Bug-223</t>
-  </si>
-  <si>
-    <t>View All navigates to Category instead of Product Listing</t>
-  </si>
-  <si>
-    <t>Bug-224</t>
-  </si>
-  <si>
-    <t>New user registration fails with server error</t>
-  </si>
-  <si>
-    <t>Bug-225</t>
-  </si>
-  <si>
-    <t>First Name and Last Name field validation does not work correctly for maximum character limit</t>
-  </si>
-  <si>
-    <t>Bug-226</t>
-  </si>
-  <si>
-    <t>User is automatically logged out after 10 minutes</t>
-  </si>
-  <si>
-    <t>Bug-227</t>
-  </si>
-  <si>
-    <t>Withdrawal screen button does not match the approved design</t>
-  </si>
-  <si>
-    <t>Bug-228</t>
-  </si>
-  <si>
-    <t>No Result Found message is not center-aligned on the Support screen</t>
-  </si>
-  <si>
-    <t>Bug-229</t>
-  </si>
-  <si>
-    <t>Transaction filter bottom sheet spacing issue</t>
-  </si>
-  <si>
-    <t>Bug-230</t>
-  </si>
-  <si>
-    <t>Price filter size is incorrect on the Product Listing screen</t>
-  </si>
-  <si>
-    <t>Bug-231</t>
-  </si>
-  <si>
-    <t>Reviewer name initials are not capitalized</t>
-  </si>
-  <si>
-    <t>Bug-232</t>
-  </si>
-  <si>
-    <t>RBF screen does not load correctly and Cart icon is displayed during loading</t>
-  </si>
-  <si>
-    <t>Bug-233</t>
-  </si>
-  <si>
-    <t>Incorrect spelling of "P2P Transfer" in Wallet</t>
-  </si>
-  <si>
-    <t>Bug-234</t>
-  </si>
-  <si>
-    <t>RBF Packs are displayed in the incorrect order and tile colors do not match the design</t>
-  </si>
-  <si>
-    <t>Bug-235</t>
-  </si>
-  <si>
-    <t>Incorrect minimum and maximum limits configured for the 50,000 RBF Pack</t>
-  </si>
-  <si>
-    <t>Bug-236</t>
-  </si>
-  <si>
-    <t>Number field does not accept input while purchasing an RBF Service Pack</t>
-  </si>
-  <si>
-    <t>Bug-237</t>
-  </si>
-  <si>
-    <t>Newly created user is assigned 0 RBF</t>
-  </si>
-  <si>
-    <t>Bug-238</t>
-  </si>
-  <si>
-    <t>New user creation fails with "Unauthorized" error</t>
-  </si>
-  <si>
-    <t>Bug-239</t>
-  </si>
-  <si>
-    <t>Plus (+) sign is missing with Service Pack amount</t>
-  </si>
-  <si>
-    <t>Bug-240</t>
-  </si>
-  <si>
-    <t>Login form data is not cleared after registering a new account and logging out</t>
-  </si>
-  <si>
-    <t>Bug-241</t>
-  </si>
-  <si>
-    <t>Incorrect spelling of "Packs" on Total Weekly Earnings card. Dashboard</t>
-  </si>
-  <si>
-    <t>Bug-242</t>
-  </si>
-  <si>
-    <t>Incorrect validation message is displayed for invalid OTP</t>
-  </si>
-  <si>
-    <t>Bug-243</t>
-  </si>
-  <si>
-    <t>First Name and Last Name fields should use initial capital keyboard</t>
-  </si>
-  <si>
-    <t>Bug-244</t>
-  </si>
-  <si>
-    <t>Unable to sign up due to incorrect internet connection error</t>
-  </si>
-  <si>
-    <t>Bug-245</t>
-  </si>
-  <si>
-    <t>Keyboard hides text fields on authentication screens</t>
-  </si>
-  <si>
-    <t>Bug-246</t>
-  </si>
-  <si>
-    <t>Onboarding screens are missing</t>
-  </si>
-  <si>
-    <t>Bug-247</t>
-  </si>
-  <si>
-    <t>Support list table is not displayed in Mobile Responsive view</t>
-  </si>
-  <si>
-    <t>Bug-248</t>
-  </si>
-  <si>
-    <t>Filter control size changes after selecting an option in Mobile Responsive view</t>
-  </si>
-  <si>
-    <t>Bug-249</t>
-  </si>
-  <si>
-    <t>Search box height does not match the approved design in Mobile Responsive view</t>
-  </si>
-  <si>
-    <t>Bug-250</t>
-  </si>
-  <si>
-    <t>Text field zooms in when focused in Mobile Responsive view</t>
-  </si>
-  <si>
-    <t>Bug-251</t>
-  </si>
-  <si>
-    <t>Admin notes are not visible to the user</t>
-  </si>
-  <si>
-    <t>Bug-252</t>
-  </si>
-  <si>
-    <t>Admin should not add notes multiple times on a support ticket</t>
-  </si>
-  <si>
-    <t>Bug-253</t>
-  </si>
-  <si>
-    <t>RBF Logs display receiver transaction history before sender transaction history</t>
-  </si>
-  <si>
-    <t>Bug-254</t>
-  </si>
-  <si>
-    <t>No actions should be allowed after a ticket is resolved</t>
-  </si>
-  <si>
-    <t>Bug-255</t>
-  </si>
-  <si>
-    <t>Incorrect transaction type is displayed in RBF Supply when purchasing a Service Pack</t>
-  </si>
-  <si>
-    <t>Bug-256</t>
-  </si>
-  <si>
-    <t>PDF export does not handle long data correctly</t>
-  </si>
-  <si>
-    <t>Bug-257</t>
-  </si>
-  <si>
-    <t>Text alignment is incorrect on Product Details and cart screen</t>
-  </si>
-  <si>
-    <t>Bug-258</t>
-  </si>
-  <si>
-    <t>Incorrect Product status values are displayed</t>
-  </si>
-  <si>
-    <t>Bug-259</t>
-  </si>
-  <si>
-    <t>Partner login flow should require email registration before password reset</t>
-  </si>
-  <si>
-    <t>Bug-260</t>
-  </si>
-  <si>
-    <t>Sub Category Edit modal does not display long data correctly</t>
-  </si>
-  <si>
-    <t>Bug-261</t>
-  </si>
-  <si>
-    <t>Long Category Title should be truncated with ellipsis</t>
-  </si>
-  <si>
-    <t>Bug-262</t>
-  </si>
-  <si>
-    <t>Category Title field should enforce a maximum limit of 150 characters</t>
-  </si>
-  <si>
-    <t>Bug-263</t>
-  </si>
-  <si>
-    <t>Volume is not displayed on Product Details screen in Admin Panel</t>
-  </si>
-  <si>
-    <t>Bug-264</t>
-  </si>
-  <si>
-    <t>Incorrect validation message is displayed when entering letters in Amount and Volume fields</t>
-  </si>
-  <si>
-    <t>Bug-265</t>
-  </si>
-  <si>
-    <t>Incorrect validation error is displayed when selecting Approved or Rejected filters on Products screen</t>
-  </si>
-  <si>
-    <t>Bug-266</t>
-  </si>
-  <si>
-    <t>Product cards are missing on the Product screen</t>
-  </si>
-  <si>
-    <t>Bug-267</t>
-  </si>
-  <si>
-    <t>Newly added Categories and Sub Categories should appear at the top of the list</t>
-  </si>
-  <si>
-    <t>Bug-268</t>
-  </si>
-  <si>
-    <t>Product amount should be displayed in Dollars instead of RBG (partner product)</t>
-  </si>
-  <si>
-    <t>Bug-269</t>
-  </si>
-  <si>
-    <t>Incorrect actions are displayed on the View Sub Category screen</t>
-  </si>
-  <si>
-    <t>Bug-270</t>
-  </si>
-  <si>
-    <t>Partner should not be able to log in when status is Pending or Suspended</t>
-  </si>
-  <si>
-    <t>Bug-271</t>
-  </si>
-  <si>
-    <t>Partner is unable to log in due to invalid OTP error</t>
-  </si>
-  <si>
-    <t>Bug-272</t>
-  </si>
-  <si>
-    <t>Scrolling is not working on the Create Partner screen</t>
-  </si>
-  <si>
-    <t>Bug-273</t>
-  </si>
-  <si>
-    <t>Incorrect page size/layout in Users PDF export</t>
-  </si>
-  <si>
-    <t>Bug-274</t>
-  </si>
-  <si>
-    <t>Incorrect export time displayed in Users PDF</t>
-  </si>
-  <si>
-    <t>Bug-275</t>
-  </si>
-  <si>
-    <t>Export Report functionality is not working</t>
-  </si>
-  <si>
-    <t>Bug-276</t>
-  </si>
-  <si>
-    <t>KYC search does not work with user's full name</t>
-  </si>
-  <si>
-    <t>Bug-277</t>
-  </si>
-  <si>
-    <t>Data is cleared when changing page size limit</t>
-  </si>
-  <si>
-    <t>Bug-278</t>
-  </si>
-  <si>
-    <t>Incorrect toast message is displayed when changing Pack status</t>
-  </si>
-  <si>
-    <t>Bug-279</t>
-  </si>
-  <si>
-    <t>Number counter should be removed from Royalty Points field</t>
-  </si>
-  <si>
-    <t>Bug-280</t>
-  </si>
-  <si>
-    <t>Service Pack values should display only two decimal places</t>
-  </si>
-  <si>
-    <t>Bug-281</t>
-  </si>
-  <si>
-    <t>Landing page -- Responsive issue</t>
-  </si>
-  <si>
-    <t>Bug-282</t>
-  </si>
-  <si>
-    <t>Landing page -- Mobile responsive – email input causes zoom and keyboard behavior issue</t>
-  </si>
-  <si>
-    <t>Bug-283</t>
-  </si>
-  <si>
-    <t>Landing page -- Favicon is missing from the application</t>
-  </si>
-  <si>
-    <t>Bug-284</t>
-  </si>
-  <si>
-    <t>Landing page -- Social media icons incorrectly navigate to top of the page</t>
-  </si>
-  <si>
-    <t>Bug-285</t>
-  </si>
-  <si>
-    <t>Landing page -- Join Waitlist link is missing in Privacy Policy and Terms &amp; Conditions</t>
-  </si>
-  <si>
-    <t>Bug-286</t>
-  </si>
-  <si>
-    <t>Landing page -- Web layout missing left and right padding</t>
-  </si>
-  <si>
-    <t>Bug-287</t>
-  </si>
-  <si>
-    <t>Landing page -- Email placeholder is not fully displayed</t>
-  </si>
-  <si>
-    <t>Bug-288</t>
-  </si>
-  <si>
-    <t>Landing page -- Logo does not have a clickable link</t>
-  </si>
-  <si>
-    <t>Bug-289</t>
-  </si>
-  <si>
-    <t>Landing page -- RBF Marketplace image position does not match the approved design</t>
-  </si>
-  <si>
-    <t>Bug-290</t>
-  </si>
-  <si>
-    <t>Landing page -- Background color does not match the approved design</t>
-  </si>
-  <si>
-    <t>Bug-291</t>
-  </si>
-  <si>
-    <t>Landing page -- Email text box color does not match the approved design</t>
-  </si>
-  <si>
-    <t>Bug-292</t>
-  </si>
-  <si>
-    <t>Landing page -- Email text is truncated in banner due to insufficient container size</t>
-  </si>
-  <si>
-    <t>Bug-293</t>
-  </si>
-  <si>
-    <t>Royal Flow Control screen does not match the approved design</t>
-  </si>
-  <si>
-    <t>Bug-294</t>
-  </si>
-  <si>
-    <t>Royal Movements Log screen does not match the approved design</t>
-  </si>
-  <si>
-    <t>Bug-295</t>
-  </si>
-  <si>
-    <t>Add Notes modal in Support Details does not match the approved design</t>
-  </si>
-  <si>
-    <t>Bug-296</t>
-  </si>
-  <si>
-    <t>Support Detail screen does not match the approved design</t>
-  </si>
-  <si>
-    <t>Bug-297</t>
-  </si>
-  <si>
-    <t>Support – Actions UI does not match the approved design</t>
-  </si>
-  <si>
-    <t>Bug-298</t>
-  </si>
-  <si>
-    <t>Support – Status colors do not match the approved design</t>
-  </si>
-  <si>
-    <t>Bug-299</t>
-  </si>
-  <si>
-    <t>KYC rejected toast message does not match design</t>
-  </si>
-  <si>
-    <t>Bug-300</t>
-  </si>
-  <si>
-    <t>Reject This KYC popup does not match the design</t>
-  </si>
-  <si>
-    <t>Bug-301</t>
-  </si>
-  <si>
-    <t>KYC status does not match the approved design</t>
-  </si>
-  <si>
-    <t>Bug-302</t>
-  </si>
-  <si>
-    <t>Withdrawal Approval user avatars do not match design</t>
-  </si>
-  <si>
-    <t>Bug-303</t>
-  </si>
-  <si>
-    <t>Module screens do not open from the top of the page</t>
-  </si>
-  <si>
-    <t>Bug-304</t>
-  </si>
-  <si>
-    <t>Suspend User toast message icon does not match design</t>
-  </si>
-  <si>
-    <t>Bug-305</t>
-  </si>
-  <si>
-    <t>Users dropdown contains duplicate Users menu item</t>
-  </si>
-  <si>
-    <t>Bug-306</t>
-  </si>
-  <si>
-    <t>Cancel button border color is incorrect in delete confirmation popup</t>
-  </si>
-  <si>
-    <t>Bug-307</t>
-  </si>
-  <si>
-    <t>Action buttons do not match approved UI design</t>
-  </si>
-  <si>
-    <t>Bug-308</t>
-  </si>
-  <si>
-    <t>Label displays unwanted space between asterisk (*) and text</t>
-  </si>
-  <si>
-    <t>Bug-309</t>
-  </si>
-  <si>
-    <t>Values do not update when changing conversion type</t>
-  </si>
-  <si>
-    <t>Bug-310</t>
-  </si>
-  <si>
-    <t>Verify Your Identity – Submit for Review button state does not match design</t>
-  </si>
-  <si>
-    <t>Bug-311</t>
-  </si>
-  <si>
-    <t>Verify Your Identity – Scroll is missing</t>
-  </si>
-  <si>
-    <t>Bug-312</t>
-  </si>
-  <si>
-    <t>Verify Your Identity – Tick position is incorrect under images</t>
-  </si>
-  <si>
-    <t>Bug-313</t>
-  </si>
-  <si>
-    <t>Verify Your Identity – Image shadow appears incorrectly</t>
-  </si>
-  <si>
-    <t>Bug-314</t>
-  </si>
-  <si>
-    <t>Verify Your Identity – National ID and Passport icon boxes mismatch design</t>
-  </si>
-  <si>
-    <t>Bug-315</t>
-  </si>
-  <si>
-    <t>FAQ arrow icon size mismatch</t>
-  </si>
-  <si>
-    <t>Bug-316</t>
-  </si>
-  <si>
-    <t>FAQ screen padding issue</t>
-  </si>
-  <si>
-    <t>Bug-317</t>
-  </si>
-  <si>
-    <t>Email field should be disabled in Edit Profile</t>
-  </si>
-  <si>
-    <t>Bug-318</t>
-  </si>
-  <si>
-    <t>Submit button design mismatch in product details</t>
-  </si>
-  <si>
-    <t>Bug-319</t>
-  </si>
-  <si>
-    <t>See all reviews button design mismatch</t>
-  </si>
-  <si>
-    <t>Bug-320</t>
-  </si>
-  <si>
-    <t>Product quantity minus button not disabled at 1</t>
-  </si>
-  <si>
-    <t>Bug-321</t>
-  </si>
-  <si>
-    <t>Product filter bottom sheet spacing issue</t>
-  </si>
-  <si>
-    <t>Bug-322</t>
-  </si>
-  <si>
-    <t>Product price unit color mismatch</t>
-  </si>
-  <si>
-    <t>Bug-323</t>
-  </si>
-  <si>
-    <t>Radio button design mismatch in filters</t>
-  </si>
-  <si>
-    <t>Bug-324</t>
-  </si>
-  <si>
-    <t>Product listing search bar design mismatch</t>
-  </si>
-  <si>
-    <t>Bug-325</t>
-  </si>
-  <si>
-    <t>My Orders filter bottom sheet spacing issue</t>
-  </si>
-  <si>
-    <t>Bug-326</t>
-  </si>
-  <si>
-    <t>My Orders search bar design mismatch</t>
-  </si>
-  <si>
-    <t>Bug-327</t>
-  </si>
-  <si>
-    <t>Support filter tick icon pixel issue</t>
-  </si>
-  <si>
-    <t>Bug-328</t>
-  </si>
-  <si>
-    <t>Support filter bottom sheet spacing issue</t>
-  </si>
-  <si>
-    <t>Bug-329</t>
-  </si>
-  <si>
-    <t>Add icon should not shown in bottom area when Create Ticket is enabled.</t>
-  </si>
-  <si>
-    <t>Bug-330</t>
-  </si>
-  <si>
-    <t>Create Ticket button hides search and filter</t>
-  </si>
-  <si>
-    <t>Bug-331</t>
-  </si>
-  <si>
-    <t>Support search bar design mismatch</t>
-  </si>
-  <si>
-    <t>Bug-332</t>
-  </si>
-  <si>
-    <t>My Referrals levels positioning incorrect</t>
-  </si>
-  <si>
-    <t>Bug-333</t>
-  </si>
-  <si>
-    <t>Refer &amp; Earn sliders misaligned</t>
-  </si>
-  <si>
-    <t>Bug-334</t>
-  </si>
-  <si>
-    <t>Bonus level card size too large</t>
-  </si>
-  <si>
-    <t>Bug-335</t>
-  </si>
-  <si>
-    <t>Refer &amp; Earn heading missing Bonus level label</t>
-  </si>
-  <si>
-    <t>Bug-336</t>
-  </si>
-  <si>
-    <t>Arrow icons size mismatch in More screen</t>
-  </si>
-  <si>
-    <t>Bug-337</t>
-  </si>
-  <si>
-    <t>More screen padding missing</t>
-  </si>
-  <si>
-    <t>Bug-338</t>
-  </si>
-  <si>
-    <t>Filter "Clear All" text casing incorrect</t>
-  </si>
-  <si>
-    <t>Bug-339</t>
-  </si>
-  <si>
-    <t>Incorrect label "withdrawal" instead of "withdrawals"</t>
-  </si>
-  <si>
-    <t>Bug-340</t>
-  </si>
-  <si>
-    <t>Transaction search bar design mismatch (text color)</t>
-  </si>
-  <si>
-    <t>Bug-341</t>
-  </si>
-  <si>
-    <t>Transaction search and filter field size mismatch</t>
-  </si>
-  <si>
-    <t>Bug-342</t>
-  </si>
-  <si>
-    <t>Transaction filter text color mismatch</t>
-  </si>
-  <si>
-    <t>Bug-343</t>
-  </si>
-  <si>
-    <t>Wallet card text color mismatch</t>
-  </si>
-  <si>
-    <t>Bug-344</t>
-  </si>
-  <si>
-    <t>Empty state missing View All in recent transactions</t>
-  </si>
-  <si>
-    <t>Bug-345</t>
-  </si>
-  <si>
-    <t>Withdraw button color mismatch in wallet</t>
-  </si>
-  <si>
-    <t>Bug-346</t>
-  </si>
-  <si>
-    <t>Wallet sliders misaligned</t>
-  </si>
-  <si>
-    <t>Bug-347</t>
-  </si>
-  <si>
-    <t>Navigation bar icons mismatch design</t>
-  </si>
-  <si>
-    <t>Bug-348</t>
-  </si>
-  <si>
-    <t>RBF confirmation screen missing</t>
-  </si>
-  <si>
-    <t>Bug-349</t>
-  </si>
-  <si>
-    <t>Connect Wallet button misaligned in bottom sheet</t>
-  </si>
-  <si>
-    <t>Bug-350</t>
-  </si>
-  <si>
-    <t>RBF service pack color mismatch</t>
-  </si>
-  <si>
-    <t>Bug-351</t>
-  </si>
-  <si>
-    <t>All Packs screen missing scroll</t>
-  </si>
-  <si>
-    <t>Bug-352</t>
-  </si>
-  <si>
-    <t>View All Packs text too small on dashboard</t>
-  </si>
-  <si>
-    <t>Bug-353</t>
-  </si>
-  <si>
-    <t>Font inconsistency across app</t>
-  </si>
-  <si>
-    <t>Bug-354</t>
-  </si>
-  <si>
-    <t>Dashboard sliders partially visible</t>
-  </si>
-  <si>
-    <t>Bug-355</t>
-  </si>
-  <si>
-    <t>Bottom navigation bar not fully visible</t>
-  </si>
-  <si>
-    <t>Bug-356</t>
-  </si>
-  <si>
-    <t>KYC screens missing</t>
-  </si>
-  <si>
-    <t>Bug-357</t>
-  </si>
-  <si>
-    <t>Verify Your Identity – Box size does not match design</t>
-  </si>
-  <si>
-    <t>Bug-358</t>
-  </si>
-  <si>
-    <t>Buttons and text misaligned at screen bottom</t>
-  </si>
-  <si>
-    <t>Bug-359</t>
-  </si>
-  <si>
-    <t>Do this later text capitalization issue</t>
-  </si>
-  <si>
-    <t>Bug-360</t>
-  </si>
-  <si>
-    <t>Email verification heading capitalization issue</t>
-  </si>
-  <si>
-    <t>Bug-361</t>
-  </si>
-  <si>
-    <t>Password eye icon does not match design</t>
-  </si>
-  <si>
-    <t>Bug-362</t>
-  </si>
-  <si>
-    <t>I am agree text incorrect on sign up screen</t>
-  </si>
-  <si>
-    <t>Bug-363</t>
-  </si>
-  <si>
-    <t>Keyboard overlaps text field</t>
-  </si>
-  <si>
-    <t>Bug-364</t>
-  </si>
-  <si>
-    <t>Validation error message is truncated</t>
-  </si>
-  <si>
-    <t>Bug-365</t>
-  </si>
-  <si>
-    <t>Validation error causes text field UI shift</t>
-  </si>
-  <si>
-    <t>Bug-366</t>
-  </si>
-  <si>
-    <t>Sign up heading font mismatch</t>
-  </si>
-  <si>
-    <t>Bug-367</t>
-  </si>
-  <si>
-    <t>Placeholder color mismatch in text fields</t>
-  </si>
-  <si>
-    <t>Bug-368</t>
-  </si>
-  <si>
-    <t>Terms &amp; Conditions and Privacy Policy links not clickable</t>
-  </si>
-  <si>
-    <t>Bug-369</t>
-  </si>
-  <si>
-    <t>Onboarding reappears after back navigation from Create Account/Login</t>
-  </si>
-  <si>
-    <t>Bug-370</t>
-  </si>
-  <si>
-    <t>Packages image mismatch on onboarding 2nd screen</t>
-  </si>
-  <si>
-    <t>Bug-371</t>
-  </si>
-  <si>
-    <t>Font size issue on onboarding screen</t>
-  </si>
-  <si>
-    <t>Bug-372</t>
-  </si>
-  <si>
-    <t>Login button color mismatch on onboarding screen</t>
-  </si>
-  <si>
-    <t>Bug-373</t>
-  </si>
-  <si>
-    <t>Conversion values between 1 and 1.9 are not displayed correctly</t>
-  </si>
-  <si>
     <t>Bug-374</t>
   </si>
   <si>
@@ -5765,66 +5765,6 @@
   </si>
   <si>
     <t>Applicable tax amounts should also be shown and calculated in RBF.</t>
-  </si>
-  <si>
-    <t>Bug-978</t>
-  </si>
-  <si>
-    <t>Bug-979</t>
-  </si>
-  <si>
-    <t>Bug-980</t>
-  </si>
-  <si>
-    <t>Bug-981</t>
-  </si>
-  <si>
-    <t>Bug-982</t>
-  </si>
-  <si>
-    <t>Bug-983</t>
-  </si>
-  <si>
-    <t>Bug-984</t>
-  </si>
-  <si>
-    <t>Bug-985</t>
-  </si>
-  <si>
-    <t>Bug-986</t>
-  </si>
-  <si>
-    <t>Bug-987</t>
-  </si>
-  <si>
-    <t>Bug-988</t>
-  </si>
-  <si>
-    <t>Bug-989</t>
-  </si>
-  <si>
-    <t>Bug-990</t>
-  </si>
-  <si>
-    <t>Bug-991</t>
-  </si>
-  <si>
-    <t>Bug-992</t>
-  </si>
-  <si>
-    <t>Bug-993</t>
-  </si>
-  <si>
-    <t>Bug-994</t>
-  </si>
-  <si>
-    <t>Bug-995</t>
-  </si>
-  <si>
-    <t>Bug-996</t>
-  </si>
-  <si>
-    <t>Bug-997</t>
   </si>
 </sst>
 </file>
@@ -5917,7 +5857,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -5953,12 +5893,6 @@
     </xf>
     <xf borderId="1" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6039,7 +5973,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C998" displayName="Table1" name="Table1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C978" displayName="Table1" name="Table1" id="1">
   <tableColumns count="3">
     <tableColumn name="Bug ID" id="1"/>
     <tableColumn name="Bug Title" id="2"/>
@@ -7602,7 +7536,7 @@
         <v>240</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C121" s="9" t="s">
         <v>82</v>
@@ -7610,10 +7544,10 @@
     </row>
     <row r="122" ht="22.5" customHeight="1">
       <c r="A122" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B122" s="7" t="s">
         <v>242</v>
-      </c>
-      <c r="B122" s="7" t="s">
-        <v>243</v>
       </c>
       <c r="C122" s="8" t="s">
         <v>82</v>
@@ -7621,10 +7555,10 @@
     </row>
     <row r="123" ht="22.5" customHeight="1">
       <c r="A123" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B123" s="5" t="s">
         <v>244</v>
-      </c>
-      <c r="B123" s="5" t="s">
-        <v>245</v>
       </c>
       <c r="C123" s="9" t="s">
         <v>82</v>
@@ -7632,10 +7566,10 @@
     </row>
     <row r="124" ht="22.5" customHeight="1">
       <c r="A124" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B124" s="7" t="s">
         <v>246</v>
-      </c>
-      <c r="B124" s="7" t="s">
-        <v>247</v>
       </c>
       <c r="C124" s="8" t="s">
         <v>82</v>
@@ -7643,10 +7577,10 @@
     </row>
     <row r="125" ht="22.5" customHeight="1">
       <c r="A125" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B125" s="5" t="s">
         <v>248</v>
-      </c>
-      <c r="B125" s="5" t="s">
-        <v>249</v>
       </c>
       <c r="C125" s="9" t="s">
         <v>82</v>
@@ -7654,10 +7588,10 @@
     </row>
     <row r="126" ht="22.5" customHeight="1">
       <c r="A126" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B126" s="7" t="s">
         <v>250</v>
-      </c>
-      <c r="B126" s="7" t="s">
-        <v>251</v>
       </c>
       <c r="C126" s="8" t="s">
         <v>82</v>
@@ -7665,10 +7599,10 @@
     </row>
     <row r="127" ht="22.5" customHeight="1">
       <c r="A127" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B127" s="5" t="s">
         <v>252</v>
-      </c>
-      <c r="B127" s="5" t="s">
-        <v>253</v>
       </c>
       <c r="C127" s="9" t="s">
         <v>82</v>
@@ -7676,10 +7610,10 @@
     </row>
     <row r="128" ht="22.5" customHeight="1">
       <c r="A128" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B128" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="B128" s="7" t="s">
-        <v>255</v>
       </c>
       <c r="C128" s="8" t="s">
         <v>82</v>
@@ -7687,10 +7621,10 @@
     </row>
     <row r="129" ht="22.5" customHeight="1">
       <c r="A129" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B129" s="5" t="s">
         <v>256</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>257</v>
       </c>
       <c r="C129" s="9" t="s">
         <v>82</v>
@@ -7698,10 +7632,10 @@
     </row>
     <row r="130" ht="22.5" customHeight="1">
       <c r="A130" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B130" s="7" t="s">
         <v>258</v>
-      </c>
-      <c r="B130" s="7" t="s">
-        <v>259</v>
       </c>
       <c r="C130" s="8" t="s">
         <v>82</v>
@@ -7709,10 +7643,10 @@
     </row>
     <row r="131" ht="22.5" customHeight="1">
       <c r="A131" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C131" s="9" t="s">
         <v>82</v>
@@ -7720,10 +7654,10 @@
     </row>
     <row r="132" ht="22.5" customHeight="1">
       <c r="A132" s="4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C132" s="8" t="s">
         <v>82</v>
@@ -7731,10 +7665,10 @@
     </row>
     <row r="133" ht="22.5" customHeight="1">
       <c r="A133" s="4" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C133" s="9" t="s">
         <v>82</v>
@@ -7742,10 +7676,10 @@
     </row>
     <row r="134" ht="22.5" customHeight="1">
       <c r="A134" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C134" s="8" t="s">
         <v>82</v>
@@ -7753,10 +7687,10 @@
     </row>
     <row r="135" ht="22.5" customHeight="1">
       <c r="A135" s="4" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C135" s="9" t="s">
         <v>82</v>
@@ -7764,10 +7698,10 @@
     </row>
     <row r="136" ht="22.5" customHeight="1">
       <c r="A136" s="4" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C136" s="8" t="s">
         <v>82</v>
@@ -7775,10 +7709,10 @@
     </row>
     <row r="137" ht="22.5" customHeight="1">
       <c r="A137" s="4" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C137" s="9" t="s">
         <v>82</v>
@@ -7786,10 +7720,10 @@
     </row>
     <row r="138" ht="22.5" customHeight="1">
       <c r="A138" s="4" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C138" s="8" t="s">
         <v>82</v>
@@ -7797,10 +7731,10 @@
     </row>
     <row r="139" ht="22.5" customHeight="1">
       <c r="A139" s="4" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C139" s="9" t="s">
         <v>82</v>
@@ -7808,10 +7742,10 @@
     </row>
     <row r="140" ht="22.5" customHeight="1">
       <c r="A140" s="4" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C140" s="8" t="s">
         <v>82</v>
@@ -7819,10 +7753,10 @@
     </row>
     <row r="141" ht="22.5" customHeight="1">
       <c r="A141" s="4" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C141" s="9" t="s">
         <v>82</v>
@@ -7830,10 +7764,10 @@
     </row>
     <row r="142" ht="22.5" customHeight="1">
       <c r="A142" s="4" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C142" s="8" t="s">
         <v>82</v>
@@ -7841,10 +7775,10 @@
     </row>
     <row r="143" ht="22.5" customHeight="1">
       <c r="A143" s="4" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C143" s="10" t="s">
         <v>82</v>
@@ -7852,10 +7786,10 @@
     </row>
     <row r="144" ht="22.5" customHeight="1">
       <c r="A144" s="4" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C144" s="11" t="s">
         <v>82</v>
@@ -7863,10 +7797,10 @@
     </row>
     <row r="145" ht="22.5" customHeight="1">
       <c r="A145" s="4" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C145" s="9" t="s">
         <v>82</v>
@@ -7874,10 +7808,10 @@
     </row>
     <row r="146" ht="22.5" customHeight="1">
       <c r="A146" s="4" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C146" s="8" t="s">
         <v>82</v>
@@ -7885,7 +7819,7 @@
     </row>
     <row r="147" ht="22.5" customHeight="1">
       <c r="A147" s="4" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>288</v>
@@ -7896,10 +7830,10 @@
     </row>
     <row r="148" ht="22.5" customHeight="1">
       <c r="A148" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C148" s="8" t="s">
         <v>82</v>
@@ -7907,10 +7841,10 @@
     </row>
     <row r="149" ht="22.5" customHeight="1">
       <c r="A149" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C149" s="9" t="s">
         <v>82</v>
@@ -7918,7 +7852,7 @@
     </row>
     <row r="150" ht="22.5" customHeight="1">
       <c r="A150" s="4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B150" s="7" t="s">
         <v>294</v>
@@ -7929,10 +7863,10 @@
     </row>
     <row r="151" ht="22.5" customHeight="1">
       <c r="A151" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B151" s="5" t="s">
         <v>296</v>
-      </c>
-      <c r="B151" s="5" t="s">
-        <v>297</v>
       </c>
       <c r="C151" s="9" t="s">
         <v>82</v>
@@ -7940,10 +7874,10 @@
     </row>
     <row r="152" ht="22.5" customHeight="1">
       <c r="A152" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B152" s="7" t="s">
         <v>298</v>
-      </c>
-      <c r="B152" s="7" t="s">
-        <v>297</v>
       </c>
       <c r="C152" s="8" t="s">
         <v>82</v>
@@ -8009,7 +7943,7 @@
         <v>309</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C158" s="8" t="s">
         <v>82</v>
@@ -8017,10 +7951,10 @@
     </row>
     <row r="159" ht="22.5" customHeight="1">
       <c r="A159" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B159" s="5" t="s">
         <v>311</v>
-      </c>
-      <c r="B159" s="5" t="s">
-        <v>312</v>
       </c>
       <c r="C159" s="9" t="s">
         <v>82</v>
@@ -8028,10 +7962,10 @@
     </row>
     <row r="160" ht="22.5" customHeight="1">
       <c r="A160" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="B160" s="7" t="s">
         <v>313</v>
-      </c>
-      <c r="B160" s="7" t="s">
-        <v>314</v>
       </c>
       <c r="C160" s="8" t="s">
         <v>82</v>
@@ -8039,10 +7973,10 @@
     </row>
     <row r="161" ht="22.5" customHeight="1">
       <c r="A161" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="B161" s="5" t="s">
         <v>315</v>
-      </c>
-      <c r="B161" s="5" t="s">
-        <v>316</v>
       </c>
       <c r="C161" s="9" t="s">
         <v>82</v>
@@ -8050,10 +7984,10 @@
     </row>
     <row r="162" ht="22.5" customHeight="1">
       <c r="A162" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="B162" s="7" t="s">
         <v>317</v>
-      </c>
-      <c r="B162" s="7" t="s">
-        <v>318</v>
       </c>
       <c r="C162" s="8" t="s">
         <v>82</v>
@@ -8061,10 +7995,10 @@
     </row>
     <row r="163" ht="22.5" customHeight="1">
       <c r="A163" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="B163" s="5" t="s">
         <v>319</v>
-      </c>
-      <c r="B163" s="5" t="s">
-        <v>320</v>
       </c>
       <c r="C163" s="9" t="s">
         <v>82</v>
@@ -8072,10 +8006,10 @@
     </row>
     <row r="164" ht="22.5" customHeight="1">
       <c r="A164" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B164" s="7" t="s">
         <v>321</v>
-      </c>
-      <c r="B164" s="7" t="s">
-        <v>322</v>
       </c>
       <c r="C164" s="8" t="s">
         <v>82</v>
@@ -8083,10 +8017,10 @@
     </row>
     <row r="165" ht="22.5" customHeight="1">
       <c r="A165" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="B165" s="5" t="s">
         <v>323</v>
-      </c>
-      <c r="B165" s="5" t="s">
-        <v>324</v>
       </c>
       <c r="C165" s="9" t="s">
         <v>82</v>
@@ -8094,10 +8028,10 @@
     </row>
     <row r="166" ht="22.5" customHeight="1">
       <c r="A166" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B166" s="7" t="s">
         <v>325</v>
-      </c>
-      <c r="B166" s="7" t="s">
-        <v>326</v>
       </c>
       <c r="C166" s="8" t="s">
         <v>82</v>
@@ -8105,10 +8039,10 @@
     </row>
     <row r="167" ht="22.5" customHeight="1">
       <c r="A167" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="B167" s="5" t="s">
         <v>327</v>
-      </c>
-      <c r="B167" s="5" t="s">
-        <v>328</v>
       </c>
       <c r="C167" s="9" t="s">
         <v>82</v>
@@ -8116,10 +8050,10 @@
     </row>
     <row r="168" ht="22.5" customHeight="1">
       <c r="A168" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="B168" s="7" t="s">
         <v>329</v>
-      </c>
-      <c r="B168" s="7" t="s">
-        <v>330</v>
       </c>
       <c r="C168" s="8" t="s">
         <v>82</v>
@@ -8127,10 +8061,10 @@
     </row>
     <row r="169" ht="22.5" customHeight="1">
       <c r="A169" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B169" s="5" t="s">
         <v>331</v>
-      </c>
-      <c r="B169" s="5" t="s">
-        <v>332</v>
       </c>
       <c r="C169" s="9" t="s">
         <v>82</v>
@@ -8138,10 +8072,10 @@
     </row>
     <row r="170" ht="22.5" customHeight="1">
       <c r="A170" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="B170" s="7" t="s">
         <v>333</v>
-      </c>
-      <c r="B170" s="7" t="s">
-        <v>334</v>
       </c>
       <c r="C170" s="8" t="s">
         <v>82</v>
@@ -8149,10 +8083,10 @@
     </row>
     <row r="171" ht="22.5" customHeight="1">
       <c r="A171" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>336</v>
+        <v>220</v>
       </c>
       <c r="C171" s="9" t="s">
         <v>82</v>
@@ -8160,10 +8094,10 @@
     </row>
     <row r="172" ht="22.5" customHeight="1">
       <c r="A172" s="4" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C172" s="8" t="s">
         <v>82</v>
@@ -8171,7 +8105,7 @@
     </row>
     <row r="173" ht="22.5" customHeight="1">
       <c r="A173" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B173" s="5" t="s">
         <v>338</v>
@@ -8182,10 +8116,10 @@
     </row>
     <row r="174" ht="22.5" customHeight="1">
       <c r="A174" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="B174" s="7" t="s">
         <v>340</v>
-      </c>
-      <c r="B174" s="7" t="s">
-        <v>341</v>
       </c>
       <c r="C174" s="8" t="s">
         <v>82</v>
@@ -8193,10 +8127,10 @@
     </row>
     <row r="175" ht="22.5" customHeight="1">
       <c r="A175" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="B175" s="5" t="s">
         <v>342</v>
-      </c>
-      <c r="B175" s="5" t="s">
-        <v>343</v>
       </c>
       <c r="C175" s="9" t="s">
         <v>82</v>
@@ -8204,10 +8138,10 @@
     </row>
     <row r="176" ht="22.5" customHeight="1">
       <c r="A176" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="B176" s="7" t="s">
         <v>344</v>
-      </c>
-      <c r="B176" s="7" t="s">
-        <v>345</v>
       </c>
       <c r="C176" s="8" t="s">
         <v>82</v>
@@ -8215,10 +8149,10 @@
     </row>
     <row r="177" ht="22.5" customHeight="1">
       <c r="A177" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="B177" s="5" t="s">
         <v>346</v>
-      </c>
-      <c r="B177" s="5" t="s">
-        <v>347</v>
       </c>
       <c r="C177" s="9" t="s">
         <v>82</v>
@@ -8226,10 +8160,10 @@
     </row>
     <row r="178" ht="22.5" customHeight="1">
       <c r="A178" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="B178" s="7" t="s">
         <v>348</v>
-      </c>
-      <c r="B178" s="7" t="s">
-        <v>349</v>
       </c>
       <c r="C178" s="8" t="s">
         <v>82</v>
@@ -8237,10 +8171,10 @@
     </row>
     <row r="179" ht="22.5" customHeight="1">
       <c r="A179" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="B179" s="5" t="s">
         <v>350</v>
-      </c>
-      <c r="B179" s="5" t="s">
-        <v>351</v>
       </c>
       <c r="C179" s="9" t="s">
         <v>82</v>
@@ -8248,10 +8182,10 @@
     </row>
     <row r="180" ht="22.5" customHeight="1">
       <c r="A180" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="B180" s="7" t="s">
         <v>352</v>
-      </c>
-      <c r="B180" s="7" t="s">
-        <v>353</v>
       </c>
       <c r="C180" s="8" t="s">
         <v>82</v>
@@ -8259,10 +8193,10 @@
     </row>
     <row r="181" ht="22.5" customHeight="1">
       <c r="A181" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="B181" s="5" t="s">
         <v>354</v>
-      </c>
-      <c r="B181" s="5" t="s">
-        <v>355</v>
       </c>
       <c r="C181" s="9" t="s">
         <v>82</v>
@@ -8270,10 +8204,10 @@
     </row>
     <row r="182" ht="22.5" customHeight="1">
       <c r="A182" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="B182" s="7" t="s">
         <v>356</v>
-      </c>
-      <c r="B182" s="7" t="s">
-        <v>357</v>
       </c>
       <c r="C182" s="8" t="s">
         <v>82</v>
@@ -8281,10 +8215,10 @@
     </row>
     <row r="183" ht="22.5" customHeight="1">
       <c r="A183" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="B183" s="5" t="s">
         <v>358</v>
-      </c>
-      <c r="B183" s="5" t="s">
-        <v>359</v>
       </c>
       <c r="C183" s="9" t="s">
         <v>82</v>
@@ -8292,10 +8226,10 @@
     </row>
     <row r="184" ht="22.5" customHeight="1">
       <c r="A184" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="B184" s="7" t="s">
         <v>360</v>
-      </c>
-      <c r="B184" s="7" t="s">
-        <v>361</v>
       </c>
       <c r="C184" s="8" t="s">
         <v>82</v>
@@ -8303,10 +8237,10 @@
     </row>
     <row r="185" ht="22.5" customHeight="1">
       <c r="A185" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="B185" s="5" t="s">
         <v>362</v>
-      </c>
-      <c r="B185" s="5" t="s">
-        <v>363</v>
       </c>
       <c r="C185" s="9" t="s">
         <v>82</v>
@@ -8314,10 +8248,10 @@
     </row>
     <row r="186" ht="22.5" customHeight="1">
       <c r="A186" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="B186" s="7" t="s">
         <v>364</v>
-      </c>
-      <c r="B186" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="C186" s="8" t="s">
         <v>82</v>
@@ -17035,229 +16969,9 @@
         <v>82</v>
       </c>
     </row>
-    <row r="979" ht="22.5" customHeight="1">
-      <c r="A979" s="4" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B979" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="C979" s="10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="980" ht="22.5" customHeight="1">
-      <c r="A980" s="4" t="s">
-        <v>1919</v>
-      </c>
-      <c r="B980" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="C980" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="981" ht="22.5" customHeight="1">
-      <c r="A981" s="4" t="s">
-        <v>1920</v>
-      </c>
-      <c r="B981" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="C981" s="10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="982" ht="22.5" customHeight="1">
-      <c r="A982" s="4" t="s">
-        <v>1921</v>
-      </c>
-      <c r="B982" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="C982" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="983" ht="22.5" customHeight="1">
-      <c r="A983" s="4" t="s">
-        <v>1922</v>
-      </c>
-      <c r="B983" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="C983" s="10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="984" ht="22.5" customHeight="1">
-      <c r="A984" s="4" t="s">
-        <v>1923</v>
-      </c>
-      <c r="B984" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="C984" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="985" ht="22.5" customHeight="1">
-      <c r="A985" s="4" t="s">
-        <v>1924</v>
-      </c>
-      <c r="B985" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="C985" s="10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="986" ht="22.5" customHeight="1">
-      <c r="A986" s="4" t="s">
-        <v>1925</v>
-      </c>
-      <c r="B986" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="C986" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="987" ht="22.5" customHeight="1">
-      <c r="A987" s="4" t="s">
-        <v>1926</v>
-      </c>
-      <c r="B987" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="C987" s="10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="988" ht="22.5" customHeight="1">
-      <c r="A988" s="4" t="s">
-        <v>1927</v>
-      </c>
-      <c r="B988" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="C988" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="989" ht="22.5" customHeight="1">
-      <c r="A989" s="4" t="s">
-        <v>1928</v>
-      </c>
-      <c r="B989" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="C989" s="10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="990" ht="22.5" customHeight="1">
-      <c r="A990" s="4" t="s">
-        <v>1929</v>
-      </c>
-      <c r="B990" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="C990" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="991" ht="22.5" customHeight="1">
-      <c r="A991" s="4" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B991" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C991" s="10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="992" ht="22.5" customHeight="1">
-      <c r="A992" s="4" t="s">
-        <v>1931</v>
-      </c>
-      <c r="B992" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="C992" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="993" ht="22.5" customHeight="1">
-      <c r="A993" s="4" t="s">
-        <v>1932</v>
-      </c>
-      <c r="B993" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="C993" s="10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="994" ht="22.5" customHeight="1">
-      <c r="A994" s="4" t="s">
-        <v>1933</v>
-      </c>
-      <c r="B994" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="C994" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="995" ht="22.5" customHeight="1">
-      <c r="A995" s="4" t="s">
-        <v>1934</v>
-      </c>
-      <c r="B995" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="C995" s="10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="996" ht="22.5" customHeight="1">
-      <c r="A996" s="4" t="s">
-        <v>1935</v>
-      </c>
-      <c r="B996" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="C996" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="997" ht="22.5" customHeight="1">
-      <c r="A997" s="4" t="s">
-        <v>1936</v>
-      </c>
-      <c r="B997" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="C997" s="10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="998" ht="22.5" customHeight="1">
-      <c r="A998" s="4" t="s">
-        <v>1937</v>
-      </c>
-      <c r="B998" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C998" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C998">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C978">
       <formula1>"Open,Done"</formula1>
     </dataValidation>
   </dataValidations>
